--- a/data/dividends_info_20260930.xlsx
+++ b/data/dividends_info_20260930.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>47.20000076293945</v>
+        <v>46.88000106811523</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1906779630195818</v>
+        <v>0.1919795178102336</v>
       </c>
       <c r="J2" t="n">
         <v>166</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>64.55000305175781</v>
+        <v>64.25</v>
       </c>
       <c r="I3" t="n">
-        <v>1.084430622627117</v>
+        <v>1.089494163424124</v>
       </c>
       <c r="J3" t="n">
         <v>145</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.5199999809265137</v>
+        <v>0.5099999904632568</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7692307974459868</v>
+        <v>0.784313740156468</v>
       </c>
       <c r="J5" t="n">
         <v>75</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>47.20000076293945</v>
+        <v>46.88000106811523</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1906779630195818</v>
+        <v>0.1919795178102336</v>
       </c>
       <c r="J6" t="n">
         <v>75</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.059999942779541</v>
+        <v>2.039999961853027</v>
       </c>
       <c r="I7" t="n">
-        <v>3.737864181496264</v>
+        <v>3.774509874503002</v>
       </c>
       <c r="J7" t="n">
         <v>54</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>50.5</v>
+        <v>49.70000076293945</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6138613861386139</v>
+        <v>0.6237424451533657</v>
       </c>
       <c r="J8" t="n">
         <v>54</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>23.94499969482422</v>
+        <v>24.02000045776367</v>
       </c>
       <c r="I9" t="n">
-        <v>1.127584061144763</v>
+        <v>1.124063259177547</v>
       </c>
       <c r="J9" t="n">
         <v>54</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>24.21999931335449</v>
+        <v>24.35000038146973</v>
       </c>
       <c r="I10" t="n">
-        <v>2.436003372116877</v>
+        <v>2.422997908652963</v>
       </c>
       <c r="J10" t="n">
         <v>54</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>12.72000026702881</v>
+        <v>12.65999984741211</v>
       </c>
       <c r="I11" t="n">
-        <v>1.65094336156844</v>
+        <v>1.658767792504572</v>
       </c>
       <c r="J11" t="n">
         <v>47</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6.010000228881836</v>
+        <v>5.96999979019165</v>
       </c>
       <c r="I12" t="n">
-        <v>3.327786894896843</v>
+        <v>3.350083869828403</v>
       </c>
       <c r="J12" t="n">
         <v>47</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6.099999904632568</v>
+        <v>6.150000095367432</v>
       </c>
       <c r="I13" t="n">
-        <v>1.147541001547219</v>
+        <v>1.138211364463692</v>
       </c>
       <c r="J13" t="n">
         <v>40</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>9.899999618530273</v>
+        <v>10.18000030517578</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6060606294135134</v>
+        <v>0.5893909450031589</v>
       </c>
       <c r="J14" t="n">
         <v>40</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>10.60999965667725</v>
+        <v>10.52000045776367</v>
       </c>
       <c r="I15" t="n">
-        <v>4.335532656784827</v>
+        <v>4.372623383875653</v>
       </c>
       <c r="J15" t="n">
         <v>26</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>8.800000190734863</v>
+        <v>8.550000190734863</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6818181670401711</v>
+        <v>0.7017543703100556</v>
       </c>
       <c r="J16" t="n">
         <v>19</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.5199999809265137</v>
+        <v>0.5099999904632568</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7692307974459868</v>
+        <v>0.784313740156468</v>
       </c>
       <c r="J17" t="n">
         <v>19</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>23.94499969482422</v>
+        <v>24.02000045776367</v>
       </c>
       <c r="I20" t="n">
-        <v>1.127584061144763</v>
+        <v>1.124063259177547</v>
       </c>
       <c r="J20" t="n">
         <v>-9</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.925999999046326</v>
+        <v>1.906999945640564</v>
       </c>
       <c r="I21" t="n">
-        <v>2.95950155909782</v>
+        <v>2.988988024373206</v>
       </c>
       <c r="J21" t="n">
         <v>-9</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>47.20000076293945</v>
+        <v>46.88000106811523</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1906779630195818</v>
+        <v>0.1919795178102336</v>
       </c>
       <c r="J22" t="n">
         <v>-9</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>94.34999847412109</v>
+        <v>93.05000305175781</v>
       </c>
       <c r="I23" t="n">
-        <v>1.40964496185424</v>
+        <v>1.429339018140822</v>
       </c>
       <c r="J23" t="n">
         <v>-9</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5.880000114440918</v>
+        <v>5.900000095367432</v>
       </c>
       <c r="I24" t="n">
-        <v>5.102040717026832</v>
+        <v>5.08474568052218</v>
       </c>
       <c r="J24" t="n">
         <v>-16</v>
@@ -1580,7 +1580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C180"/>
+  <dimension ref="A1:C170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1620,7 +1620,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1637,7 +1637,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1654,7 +1654,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1671,7 +1671,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1681,14 +1681,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>OPT S.p.A.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1722,7 +1722,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OPT S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1739,7 +1739,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1749,14 +1749,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1773,7 +1773,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1790,7 +1790,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1817,14 +1817,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1841,7 +1841,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,14 +1851,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1868,14 +1868,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1892,7 +1892,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1909,7 +1909,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1926,7 +1926,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1936,14 +1936,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1977,7 +1977,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1987,14 +1987,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2011,7 +2011,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2062,7 +2062,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2079,7 +2079,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2096,7 +2096,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2113,7 +2113,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2130,7 +2130,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2147,7 +2147,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2164,7 +2164,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2198,7 +2198,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2215,7 +2215,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2225,14 +2225,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2249,7 +2249,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2266,7 +2266,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2283,7 +2283,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2317,7 +2317,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2334,7 +2334,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2351,7 +2351,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2361,14 +2361,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2385,7 +2385,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>Alia Mentis S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2402,7 +2402,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2419,7 +2419,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2453,7 +2453,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2470,7 +2470,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2480,14 +2480,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2504,7 +2504,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Alia Mentis S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2538,7 +2538,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2555,7 +2555,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2572,7 +2572,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2589,7 +2589,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2606,7 +2606,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2640,7 +2640,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2657,7 +2657,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2674,7 +2674,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2708,7 +2708,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2718,14 +2718,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2735,138 +2735,138 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>RT&amp;L S.P.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>LANDI RENZO S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2878,46 +2878,46 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>First Point S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>RT&amp;L S.P.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2929,29 +2929,29 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>LANDI RENZO S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2963,29 +2963,29 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>SB Annual Report</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2997,29 +2997,29 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3031,12 +3031,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3048,12 +3048,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3065,29 +3065,29 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3099,12 +3099,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3116,12 +3116,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3133,29 +3133,29 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SB Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3167,29 +3167,29 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3201,12 +3201,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3218,97 +3218,97 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3320,46 +3320,46 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3371,80 +3371,80 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3456,29 +3456,29 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3490,46 +3490,46 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3541,46 +3541,46 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3592,29 +3592,29 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3626,12 +3626,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3643,12 +3643,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3660,63 +3660,63 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3728,12 +3728,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3745,29 +3745,29 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3779,46 +3779,46 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>LANDI RENZO S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3830,80 +3830,80 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3915,80 +3915,80 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>LANDI RENZO S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4000,97 +4000,97 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4102,29 +4102,29 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4136,7 +4136,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4146,14 +4146,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4163,19 +4163,19 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4187,12 +4187,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4204,12 +4204,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4221,29 +4221,29 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4255,29 +4255,29 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4289,29 +4289,29 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4323,24 +4323,24 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4357,12 +4357,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4374,12 +4374,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4391,12 +4391,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4408,12 +4408,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4425,219 +4425,49 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Prysmian S.p.A.</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Seri Industrial S.p.A.</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>AMPLIFON S.p.A.</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>VNE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>BIESSE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Basic Net S.p.A.</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>OPS ECOM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>SOGES GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
         <is>
           <t>Additional Periodic Financial Information</t>
         </is>
@@ -4667,418 +4497,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BIESSE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Basic Net S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CIRCLE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DBA GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>FIDIA S.p.A</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>GPI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>GREEN OLEO S.p.A</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>GREEN OLEO S.p.A</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>GREEN OLEO S.p.A</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Magis S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>OPS ECOM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>ORANGE MEDIA GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>RT&amp;L S.P.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>S.S. Lazio S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>SB Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>SOGES GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Tecno S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Tecno S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Tecno S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>VNE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>